--- a/00-esmagadora-modelo/dados_sujos/apontamentos_mensais/producao_2025_02.xlsx
+++ b/00-esmagadora-modelo/dados_sujos/apontamentos_mensais/producao_2025_02.xlsx
@@ -480,25 +480,25 @@
         <v>45689</v>
       </c>
       <c r="B5" t="n">
-        <v>696.28</v>
+        <v>1464.91</v>
       </c>
       <c r="C5" t="n">
-        <v>11.24</v>
+        <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>508.09</v>
+        <v>1062.02</v>
       </c>
       <c r="E5" t="n">
-        <v>139.35</v>
+        <v>292.58</v>
       </c>
       <c r="F5" t="n">
-        <v>1516</v>
+        <v>1238</v>
       </c>
       <c r="G5" t="n">
-        <v>208691</v>
+        <v>391010</v>
       </c>
       <c r="H5" t="n">
-        <v>32155</v>
+        <v>63790</v>
       </c>
     </row>
     <row r="6">
@@ -506,25 +506,25 @@
         <v>45690</v>
       </c>
       <c r="B6" t="n">
-        <v>722.3200000000001</v>
+        <v>1474.28</v>
       </c>
       <c r="C6" t="n">
-        <v>11.75</v>
+        <v>23.62</v>
       </c>
       <c r="D6" t="n">
-        <v>527.95</v>
+        <v>1068.64</v>
       </c>
       <c r="E6" t="n">
-        <v>140.07</v>
+        <v>284.12</v>
       </c>
       <c r="F6" t="n">
-        <v>1476</v>
+        <v>1242</v>
       </c>
       <c r="G6" t="n">
-        <v>209258</v>
+        <v>365502</v>
       </c>
       <c r="H6" t="n">
-        <v>32573</v>
+        <v>71386</v>
       </c>
     </row>
     <row r="7">
@@ -532,25 +532,25 @@
         <v>45691</v>
       </c>
       <c r="B7" t="n">
-        <v>1466.77</v>
+        <v>1499.07</v>
       </c>
       <c r="C7" t="n">
-        <v>23.42</v>
+        <v>23.84</v>
       </c>
       <c r="D7" t="n">
-        <v>1063.61</v>
+        <v>1093.63</v>
       </c>
       <c r="E7" t="n">
-        <v>289.59</v>
+        <v>306.74</v>
       </c>
       <c r="F7" t="n">
-        <v>2411</v>
+        <v>1182</v>
       </c>
       <c r="G7" t="n">
-        <v>373808</v>
+        <v>446464</v>
       </c>
       <c r="H7" t="n">
-        <v>64772</v>
+        <v>70446</v>
       </c>
     </row>
     <row r="8">
@@ -558,25 +558,25 @@
         <v>45692</v>
       </c>
       <c r="B8" t="n">
-        <v>1501.12</v>
+        <v>1566.99</v>
       </c>
       <c r="C8" t="n">
-        <v>24</v>
+        <v>23.39</v>
       </c>
       <c r="D8" t="n">
-        <v>1094.8</v>
+        <v>1133.47</v>
       </c>
       <c r="E8" t="n">
-        <v>301.31</v>
+        <v>319.01</v>
       </c>
       <c r="F8" t="n">
-        <v>2249</v>
+        <v>1594</v>
       </c>
       <c r="G8" t="n">
-        <v>393887</v>
+        <v>417269</v>
       </c>
       <c r="H8" t="n">
-        <v>71384</v>
+        <v>67683</v>
       </c>
     </row>
     <row r="9">
@@ -584,25 +584,25 @@
         <v>45693</v>
       </c>
       <c r="B9" t="n">
-        <v>1378.17</v>
+        <v>1423.17</v>
       </c>
       <c r="C9" t="n">
-        <v>22.03</v>
+        <v>24</v>
       </c>
       <c r="D9" t="n">
-        <v>1004.71</v>
+        <v>1039.89</v>
       </c>
       <c r="E9" t="n">
-        <v>274.47</v>
+        <v>296.2</v>
       </c>
       <c r="F9" t="n">
-        <v>1857</v>
+        <v>1243</v>
       </c>
       <c r="G9" t="n">
-        <v>380511</v>
+        <v>395706</v>
       </c>
       <c r="H9" t="n">
-        <v>61375</v>
+        <v>64474</v>
       </c>
     </row>
     <row r="10">
@@ -610,25 +610,25 @@
         <v>45694</v>
       </c>
       <c r="B10" t="n">
-        <v>1522.26</v>
+        <v>1456.14</v>
       </c>
       <c r="C10" t="n">
         <v>24</v>
       </c>
       <c r="D10" t="n">
-        <v>1108.06</v>
+        <v>1055.99</v>
       </c>
       <c r="E10" t="n">
-        <v>300.11</v>
+        <v>295.42</v>
       </c>
       <c r="F10" t="n">
-        <v>2432</v>
+        <v>1535</v>
       </c>
       <c r="G10" t="n">
-        <v>380834</v>
+        <v>382619</v>
       </c>
       <c r="H10" t="n">
-        <v>71223</v>
+        <v>65492</v>
       </c>
     </row>
     <row r="11">
@@ -636,25 +636,25 @@
         <v>45695</v>
       </c>
       <c r="B11" t="n">
-        <v>1337.61</v>
+        <v>1484.45</v>
       </c>
       <c r="C11" t="n">
-        <v>20.75</v>
+        <v>24</v>
       </c>
       <c r="D11" t="n">
-        <v>975.22</v>
+        <v>1071.48</v>
       </c>
       <c r="E11" t="n">
-        <v>271.67</v>
+        <v>289.2</v>
       </c>
       <c r="F11" t="n">
-        <v>1841</v>
+        <v>1427</v>
       </c>
       <c r="G11" t="n">
-        <v>358537</v>
+        <v>358838</v>
       </c>
       <c r="H11" t="n">
-        <v>58095</v>
+        <v>65625</v>
       </c>
     </row>
     <row r="12">
@@ -662,25 +662,25 @@
         <v>45696</v>
       </c>
       <c r="B12" t="n">
-        <v>1608</v>
+        <v>1542.28</v>
       </c>
       <c r="C12" t="n">
         <v>24</v>
       </c>
       <c r="D12" t="n">
-        <v>1168.45</v>
+        <v>1116.63</v>
       </c>
       <c r="E12" t="n">
-        <v>309.56</v>
+        <v>314.6</v>
       </c>
       <c r="F12" t="n">
-        <v>2275</v>
+        <v>1549</v>
       </c>
       <c r="G12" t="n">
-        <v>424003</v>
+        <v>393738</v>
       </c>
       <c r="H12" t="n">
-        <v>71792</v>
+        <v>68252</v>
       </c>
     </row>
     <row r="13">
@@ -688,25 +688,25 @@
         <v>45697</v>
       </c>
       <c r="B13" t="n">
-        <v>1204.78</v>
+        <v>1533.19</v>
       </c>
       <c r="C13" t="n">
-        <v>19.79</v>
+        <v>24</v>
       </c>
       <c r="D13" t="n">
-        <v>871.6799999999999</v>
+        <v>1106.05</v>
       </c>
       <c r="E13" t="n">
-        <v>237.53</v>
+        <v>300.89</v>
       </c>
       <c r="F13" t="n">
-        <v>2096</v>
+        <v>1490</v>
       </c>
       <c r="G13" t="n">
-        <v>328192</v>
+        <v>381006</v>
       </c>
       <c r="H13" t="n">
-        <v>54008</v>
+        <v>69765</v>
       </c>
     </row>
     <row r="14">
@@ -714,25 +714,25 @@
         <v>45698</v>
       </c>
       <c r="B14" t="n">
-        <v>601.92</v>
+        <v>624.1799999999999</v>
       </c>
       <c r="C14" t="n">
         <v>10.23</v>
       </c>
       <c r="D14" t="n">
-        <v>432.47</v>
+        <v>452.54</v>
       </c>
       <c r="E14" t="n">
-        <v>123.6</v>
+        <v>122.57</v>
       </c>
       <c r="F14" t="n">
-        <v>1141</v>
+        <v>726</v>
       </c>
       <c r="G14" t="n">
-        <v>174164</v>
+        <v>163000</v>
       </c>
       <c r="H14" t="n">
-        <v>28848</v>
+        <v>28728</v>
       </c>
     </row>
     <row r="15">
@@ -740,25 +740,25 @@
         <v>45699</v>
       </c>
       <c r="B15" t="n">
-        <v>1044.61</v>
+        <v>1425.27</v>
       </c>
       <c r="C15" t="n">
-        <v>17.48</v>
+        <v>24</v>
       </c>
       <c r="D15" t="n">
-        <v>764.42</v>
+        <v>1034.83</v>
       </c>
       <c r="E15" t="n">
-        <v>211.45</v>
+        <v>277.95</v>
       </c>
       <c r="F15" t="n">
-        <v>1777</v>
+        <v>1385</v>
       </c>
       <c r="G15" t="n">
-        <v>308532</v>
+        <v>330607</v>
       </c>
       <c r="H15" t="n">
-        <v>50330</v>
+        <v>62698</v>
       </c>
     </row>
     <row r="16">
@@ -766,25 +766,25 @@
         <v>45700</v>
       </c>
       <c r="B16" t="n">
-        <v>1483.03</v>
+        <v>1437.64</v>
       </c>
       <c r="C16" t="n">
         <v>24</v>
       </c>
       <c r="D16" t="n">
-        <v>1068.21</v>
+        <v>1051.15</v>
       </c>
       <c r="E16" t="n">
-        <v>293.26</v>
+        <v>293.92</v>
       </c>
       <c r="F16" t="n">
-        <v>1982</v>
+        <v>1658</v>
       </c>
       <c r="G16" t="n">
-        <v>376088</v>
+        <v>373379</v>
       </c>
       <c r="H16" t="n">
-        <v>67360</v>
+        <v>64689</v>
       </c>
     </row>
     <row r="17">
@@ -792,25 +792,25 @@
         <v>45701</v>
       </c>
       <c r="B17" t="n">
-        <v>1563.35</v>
+        <v>1397.6</v>
       </c>
       <c r="C17" t="n">
-        <v>24</v>
+        <v>22.01</v>
       </c>
       <c r="D17" t="n">
-        <v>1136.38</v>
+        <v>1016.42</v>
       </c>
       <c r="E17" t="n">
-        <v>310.97</v>
+        <v>270.02</v>
       </c>
       <c r="F17" t="n">
-        <v>2817</v>
+        <v>1163</v>
       </c>
       <c r="G17" t="n">
-        <v>451474</v>
+        <v>385725</v>
       </c>
       <c r="H17" t="n">
-        <v>69055</v>
+        <v>66363</v>
       </c>
     </row>
     <row r="18">
@@ -818,25 +818,25 @@
         <v>45702</v>
       </c>
       <c r="B18" t="n">
-        <v>1450.58</v>
+        <v>1526.88</v>
       </c>
       <c r="C18" t="n">
         <v>24</v>
       </c>
       <c r="D18" t="n">
-        <v>1045.09</v>
+        <v>1111.87</v>
       </c>
       <c r="E18" t="n">
-        <v>292.31</v>
+        <v>301.18</v>
       </c>
       <c r="F18" t="n">
-        <v>2379</v>
+        <v>1291</v>
       </c>
       <c r="G18" t="n">
-        <v>355232</v>
+        <v>377713</v>
       </c>
       <c r="H18" t="n">
-        <v>59417</v>
+        <v>69512</v>
       </c>
     </row>
     <row r="19">
@@ -844,25 +844,25 @@
         <v>45703</v>
       </c>
       <c r="B19" t="n">
-        <v>1522.57</v>
+        <v>1476.05</v>
       </c>
       <c r="C19" t="n">
         <v>24</v>
       </c>
       <c r="D19" t="n">
-        <v>1102.36</v>
+        <v>1072.39</v>
       </c>
       <c r="E19" t="n">
-        <v>300.97</v>
+        <v>293.04</v>
       </c>
       <c r="F19" t="n">
-        <v>1942</v>
+        <v>1460</v>
       </c>
       <c r="G19" t="n">
-        <v>388657</v>
+        <v>381798</v>
       </c>
       <c r="H19" t="n">
-        <v>70093</v>
+        <v>62635</v>
       </c>
     </row>
     <row r="20">
@@ -870,25 +870,25 @@
         <v>45704</v>
       </c>
       <c r="B20" t="n">
-        <v>1427.33</v>
+        <v>1558.34</v>
       </c>
       <c r="C20" t="n">
-        <v>22.72</v>
+        <v>24</v>
       </c>
       <c r="D20" t="n">
-        <v>1039.78</v>
+        <v>1131.91</v>
       </c>
       <c r="E20" t="n">
-        <v>290.37</v>
+        <v>312.01</v>
       </c>
       <c r="F20" t="n">
-        <v>1902</v>
+        <v>1414</v>
       </c>
       <c r="G20" t="n">
-        <v>395836</v>
+        <v>398511</v>
       </c>
       <c r="H20" t="n">
-        <v>61064</v>
+        <v>75464</v>
       </c>
     </row>
     <row r="21">
@@ -896,25 +896,25 @@
         <v>45705</v>
       </c>
       <c r="B21" t="n">
-        <v>533.29</v>
+        <v>1480.61</v>
       </c>
       <c r="C21" t="n">
-        <v>8.9</v>
+        <v>23.14</v>
       </c>
       <c r="D21" t="n">
-        <v>387.77</v>
+        <v>1064.66</v>
       </c>
       <c r="E21" t="n">
-        <v>103.2</v>
+        <v>291.83</v>
       </c>
       <c r="F21" t="n">
-        <v>954</v>
+        <v>1240</v>
       </c>
       <c r="G21" t="n">
-        <v>162039</v>
+        <v>384387</v>
       </c>
       <c r="H21" t="n">
-        <v>24655</v>
+        <v>68124</v>
       </c>
     </row>
     <row r="22">
@@ -922,25 +922,25 @@
         <v>45706</v>
       </c>
       <c r="B22" t="n">
-        <v>812.45</v>
+        <v>1491.77</v>
       </c>
       <c r="C22" t="n">
-        <v>13.89</v>
+        <v>24</v>
       </c>
       <c r="D22" t="n">
-        <v>589.51</v>
+        <v>1090.53</v>
       </c>
       <c r="E22" t="n">
-        <v>162.01</v>
+        <v>299.55</v>
       </c>
       <c r="F22" t="n">
-        <v>1427</v>
+        <v>1372</v>
       </c>
       <c r="G22" t="n">
-        <v>220430</v>
+        <v>385157</v>
       </c>
       <c r="H22" t="n">
-        <v>38141</v>
+        <v>69491</v>
       </c>
     </row>
     <row r="23">
@@ -948,25 +948,25 @@
         <v>45707</v>
       </c>
       <c r="B23" t="n">
-        <v>1491.51</v>
+        <v>1385.97</v>
       </c>
       <c r="C23" t="n">
-        <v>24</v>
+        <v>22.81</v>
       </c>
       <c r="D23" t="n">
-        <v>1067.98</v>
+        <v>1003.26</v>
       </c>
       <c r="E23" t="n">
-        <v>285.65</v>
+        <v>279.44</v>
       </c>
       <c r="F23" t="n">
-        <v>2246</v>
+        <v>1352</v>
       </c>
       <c r="G23" t="n">
-        <v>392018</v>
+        <v>353678</v>
       </c>
       <c r="H23" t="n">
-        <v>67507</v>
+        <v>66130</v>
       </c>
     </row>
     <row r="24">
@@ -974,25 +974,25 @@
         <v>45708</v>
       </c>
       <c r="B24" t="n">
-        <v>1390.28</v>
+        <v>1444.58</v>
       </c>
       <c r="C24" t="n">
         <v>24</v>
       </c>
       <c r="D24" t="n">
-        <v>999.99</v>
+        <v>1042.01</v>
       </c>
       <c r="E24" t="n">
-        <v>266.55</v>
+        <v>287.73</v>
       </c>
       <c r="F24" t="n">
-        <v>1667</v>
+        <v>1310</v>
       </c>
       <c r="G24" t="n">
-        <v>354896</v>
+        <v>365059</v>
       </c>
       <c r="H24" t="n">
-        <v>61789</v>
+        <v>65656</v>
       </c>
     </row>
     <row r="25">
@@ -1000,25 +1000,25 @@
         <v>45709</v>
       </c>
       <c r="B25" t="n">
-        <v>1305.82</v>
+        <v>1304.84</v>
       </c>
       <c r="C25" t="n">
-        <v>22.13</v>
+        <v>20.96</v>
       </c>
       <c r="D25" t="n">
-        <v>949.5</v>
+        <v>955.5599999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>264.58</v>
+        <v>267.45</v>
       </c>
       <c r="F25" t="n">
-        <v>2096</v>
+        <v>1429</v>
       </c>
       <c r="G25" t="n">
-        <v>337498</v>
+        <v>328615</v>
       </c>
       <c r="H25" t="n">
-        <v>57737</v>
+        <v>57148</v>
       </c>
     </row>
     <row r="26">
@@ -1026,25 +1026,25 @@
         <v>45710</v>
       </c>
       <c r="B26" t="n">
-        <v>1487.63</v>
+        <v>1532.93</v>
       </c>
       <c r="C26" t="n">
         <v>24</v>
       </c>
       <c r="D26" t="n">
-        <v>1081.26</v>
+        <v>1111.45</v>
       </c>
       <c r="E26" t="n">
-        <v>294.62</v>
+        <v>305.46</v>
       </c>
       <c r="F26" t="n">
-        <v>2402</v>
+        <v>1105</v>
       </c>
       <c r="G26" t="n">
-        <v>389685</v>
+        <v>364976</v>
       </c>
       <c r="H26" t="n">
-        <v>69984</v>
+        <v>73309</v>
       </c>
     </row>
     <row r="27">
@@ -1052,25 +1052,25 @@
         <v>45711</v>
       </c>
       <c r="B27" t="n">
-        <v>1473.34</v>
+        <v>1503.89</v>
       </c>
       <c r="C27" t="n">
-        <v>23.42</v>
+        <v>23.88</v>
       </c>
       <c r="D27" t="n">
-        <v>1073.18</v>
+        <v>1085.25</v>
       </c>
       <c r="E27" t="n">
-        <v>281.28</v>
+        <v>297.24</v>
       </c>
       <c r="F27" t="n">
-        <v>2299</v>
+        <v>1377</v>
       </c>
       <c r="G27" t="n">
-        <v>431080</v>
+        <v>397353</v>
       </c>
       <c r="H27" t="n">
-        <v>63968</v>
+        <v>67422</v>
       </c>
     </row>
     <row r="28">
@@ -1078,25 +1078,25 @@
         <v>45712</v>
       </c>
       <c r="B28" t="n">
-        <v>1608</v>
+        <v>1385.89</v>
       </c>
       <c r="C28" t="n">
-        <v>24</v>
+        <v>22.43</v>
       </c>
       <c r="D28" t="n">
-        <v>1172.26</v>
+        <v>1010.34</v>
       </c>
       <c r="E28" t="n">
-        <v>325.83</v>
+        <v>272.99</v>
       </c>
       <c r="F28" t="n">
-        <v>3179</v>
+        <v>1283</v>
       </c>
       <c r="G28" t="n">
-        <v>477338</v>
+        <v>372286</v>
       </c>
       <c r="H28" t="n">
-        <v>72579</v>
+        <v>66230</v>
       </c>
     </row>
     <row r="29">
@@ -1104,25 +1104,25 @@
         <v>45713</v>
       </c>
       <c r="B29" t="n">
-        <v>1554.13</v>
+        <v>1547.09</v>
       </c>
       <c r="C29" t="n">
         <v>24</v>
       </c>
       <c r="D29" t="n">
-        <v>1125.52</v>
+        <v>1114.13</v>
       </c>
       <c r="E29" t="n">
-        <v>305.74</v>
+        <v>298.72</v>
       </c>
       <c r="F29" t="n">
-        <v>2365</v>
+        <v>1683</v>
       </c>
       <c r="G29" t="n">
-        <v>397532</v>
+        <v>393803</v>
       </c>
       <c r="H29" t="n">
-        <v>76719</v>
+        <v>67509</v>
       </c>
     </row>
     <row r="30">
@@ -1130,25 +1130,25 @@
         <v>45714</v>
       </c>
       <c r="B30" t="n">
-        <v>1411.19</v>
+        <v>1388.34</v>
       </c>
       <c r="C30" t="n">
-        <v>23.63</v>
+        <v>23.12</v>
       </c>
       <c r="D30" t="n">
-        <v>1026.24</v>
+        <v>999.8200000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>282.03</v>
+        <v>275.53</v>
       </c>
       <c r="F30" t="n">
-        <v>1846</v>
+        <v>1361</v>
       </c>
       <c r="G30" t="n">
-        <v>353518</v>
+        <v>333373</v>
       </c>
       <c r="H30" t="n">
-        <v>63079</v>
+        <v>61375</v>
       </c>
     </row>
     <row r="31">
@@ -1156,25 +1156,25 @@
         <v>45715</v>
       </c>
       <c r="B31" t="n">
-        <v>1449.98</v>
+        <v>1410.29</v>
       </c>
       <c r="C31" t="n">
         <v>24</v>
       </c>
       <c r="D31" t="n">
-        <v>1056.53</v>
+        <v>1022.02</v>
       </c>
       <c r="E31" t="n">
-        <v>289.66</v>
+        <v>277.91</v>
       </c>
       <c r="F31" t="n">
-        <v>2669</v>
+        <v>1301</v>
       </c>
       <c r="G31" t="n">
-        <v>385497</v>
+        <v>364839</v>
       </c>
       <c r="H31" t="n">
-        <v>65278</v>
+        <v>62313</v>
       </c>
     </row>
     <row r="32">
@@ -1182,25 +1182,25 @@
         <v>45716</v>
       </c>
       <c r="B32" t="n">
-        <v>1495.14</v>
+        <v>1501.22</v>
       </c>
       <c r="C32" t="n">
-        <v>24</v>
+        <v>23.44</v>
       </c>
       <c r="D32" t="n">
-        <v>1084.96</v>
+        <v>1088.43</v>
       </c>
       <c r="E32" t="n">
-        <v>296.06</v>
+        <v>296.27</v>
       </c>
       <c r="F32" t="n">
-        <v>2075</v>
+        <v>1324</v>
       </c>
       <c r="G32" t="n">
-        <v>389375</v>
+        <v>430288</v>
       </c>
       <c r="H32" t="n">
-        <v>68081</v>
+        <v>70682</v>
       </c>
     </row>
     <row r="34">
@@ -1210,25 +1210,25 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>36543.46000000001</v>
+        <v>40267.85999999999</v>
       </c>
       <c r="C34" t="n">
-        <v>587.38</v>
+        <v>646.87</v>
       </c>
       <c r="D34" t="n">
-        <v>26525.98</v>
+        <v>29206.37</v>
       </c>
       <c r="E34" t="n">
-        <v>7243.799999999999</v>
+        <v>8019.57</v>
       </c>
       <c r="F34" t="n">
-        <v>57318</v>
+        <v>37734</v>
       </c>
       <c r="G34" t="n">
-        <v>9798610</v>
+        <v>10416699</v>
       </c>
       <c r="H34" t="n">
-        <v>1653061</v>
+        <v>1832391</v>
       </c>
     </row>
   </sheetData>

--- a/00-esmagadora-modelo/dados_sujos/apontamentos_mensais/producao_2025_02.xlsx
+++ b/00-esmagadora-modelo/dados_sujos/apontamentos_mensais/producao_2025_02.xlsx
@@ -480,25 +480,25 @@
         <v>45689</v>
       </c>
       <c r="B5" t="n">
-        <v>1464.91</v>
+        <v>1435.51</v>
       </c>
       <c r="C5" t="n">
         <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>1062.02</v>
+        <v>1042.02</v>
       </c>
       <c r="E5" t="n">
-        <v>292.58</v>
+        <v>279.33</v>
       </c>
       <c r="F5" t="n">
-        <v>1238</v>
+        <v>1455</v>
       </c>
       <c r="G5" t="n">
-        <v>391010</v>
+        <v>378684</v>
       </c>
       <c r="H5" t="n">
-        <v>63790</v>
+        <v>60754</v>
       </c>
     </row>
     <row r="6">
@@ -506,25 +506,25 @@
         <v>45690</v>
       </c>
       <c r="B6" t="n">
-        <v>1474.28</v>
+        <v>1473.57</v>
       </c>
       <c r="C6" t="n">
-        <v>23.62</v>
+        <v>24</v>
       </c>
       <c r="D6" t="n">
-        <v>1068.64</v>
+        <v>1072.76</v>
       </c>
       <c r="E6" t="n">
-        <v>284.12</v>
+        <v>287.51</v>
       </c>
       <c r="F6" t="n">
-        <v>1242</v>
+        <v>1222</v>
       </c>
       <c r="G6" t="n">
-        <v>365502</v>
+        <v>384075</v>
       </c>
       <c r="H6" t="n">
-        <v>71386</v>
+        <v>68755</v>
       </c>
     </row>
     <row r="7">
@@ -532,25 +532,25 @@
         <v>45691</v>
       </c>
       <c r="B7" t="n">
-        <v>1499.07</v>
+        <v>1548.04</v>
       </c>
       <c r="C7" t="n">
-        <v>23.84</v>
+        <v>24</v>
       </c>
       <c r="D7" t="n">
-        <v>1093.63</v>
+        <v>1117.5</v>
       </c>
       <c r="E7" t="n">
-        <v>306.74</v>
+        <v>304.97</v>
       </c>
       <c r="F7" t="n">
-        <v>1182</v>
+        <v>1115</v>
       </c>
       <c r="G7" t="n">
-        <v>446464</v>
+        <v>422265</v>
       </c>
       <c r="H7" t="n">
-        <v>70446</v>
+        <v>69508</v>
       </c>
     </row>
     <row r="8">
@@ -558,25 +558,25 @@
         <v>45692</v>
       </c>
       <c r="B8" t="n">
-        <v>1566.99</v>
+        <v>1361.63</v>
       </c>
       <c r="C8" t="n">
-        <v>23.39</v>
+        <v>23.63</v>
       </c>
       <c r="D8" t="n">
-        <v>1133.47</v>
+        <v>990.9</v>
       </c>
       <c r="E8" t="n">
-        <v>319.01</v>
+        <v>266</v>
       </c>
       <c r="F8" t="n">
-        <v>1594</v>
+        <v>1181</v>
       </c>
       <c r="G8" t="n">
-        <v>417269</v>
+        <v>372123</v>
       </c>
       <c r="H8" t="n">
-        <v>67683</v>
+        <v>66271</v>
       </c>
     </row>
     <row r="9">
@@ -584,25 +584,25 @@
         <v>45693</v>
       </c>
       <c r="B9" t="n">
-        <v>1423.17</v>
+        <v>1433.42</v>
       </c>
       <c r="C9" t="n">
         <v>24</v>
       </c>
       <c r="D9" t="n">
-        <v>1039.89</v>
+        <v>1041.53</v>
       </c>
       <c r="E9" t="n">
-        <v>296.2</v>
+        <v>284.38</v>
       </c>
       <c r="F9" t="n">
-        <v>1243</v>
+        <v>1088</v>
       </c>
       <c r="G9" t="n">
-        <v>395706</v>
+        <v>351554</v>
       </c>
       <c r="H9" t="n">
-        <v>64474</v>
+        <v>65489</v>
       </c>
     </row>
     <row r="10">
@@ -610,25 +610,25 @@
         <v>45694</v>
       </c>
       <c r="B10" t="n">
-        <v>1456.14</v>
+        <v>1544.39</v>
       </c>
       <c r="C10" t="n">
-        <v>24</v>
+        <v>23.37</v>
       </c>
       <c r="D10" t="n">
-        <v>1055.99</v>
+        <v>1121.3</v>
       </c>
       <c r="E10" t="n">
-        <v>295.42</v>
+        <v>315.27</v>
       </c>
       <c r="F10" t="n">
-        <v>1535</v>
+        <v>1247</v>
       </c>
       <c r="G10" t="n">
-        <v>382619</v>
+        <v>390286</v>
       </c>
       <c r="H10" t="n">
-        <v>65492</v>
+        <v>68352</v>
       </c>
     </row>
     <row r="11">
@@ -636,25 +636,25 @@
         <v>45695</v>
       </c>
       <c r="B11" t="n">
-        <v>1484.45</v>
+        <v>1548.35</v>
       </c>
       <c r="C11" t="n">
         <v>24</v>
       </c>
       <c r="D11" t="n">
-        <v>1071.48</v>
+        <v>1122.86</v>
       </c>
       <c r="E11" t="n">
-        <v>289.2</v>
+        <v>306.53</v>
       </c>
       <c r="F11" t="n">
-        <v>1427</v>
+        <v>1859</v>
       </c>
       <c r="G11" t="n">
-        <v>358838</v>
+        <v>415991</v>
       </c>
       <c r="H11" t="n">
-        <v>65625</v>
+        <v>68112</v>
       </c>
     </row>
     <row r="12">
@@ -662,25 +662,25 @@
         <v>45696</v>
       </c>
       <c r="B12" t="n">
-        <v>1542.28</v>
+        <v>1473.16</v>
       </c>
       <c r="C12" t="n">
         <v>24</v>
       </c>
       <c r="D12" t="n">
-        <v>1116.63</v>
+        <v>1066.17</v>
       </c>
       <c r="E12" t="n">
-        <v>314.6</v>
+        <v>285.91</v>
       </c>
       <c r="F12" t="n">
-        <v>1549</v>
+        <v>1447</v>
       </c>
       <c r="G12" t="n">
-        <v>393738</v>
+        <v>366127</v>
       </c>
       <c r="H12" t="n">
-        <v>68252</v>
+        <v>64950</v>
       </c>
     </row>
     <row r="13">
@@ -688,25 +688,25 @@
         <v>45697</v>
       </c>
       <c r="B13" t="n">
-        <v>1533.19</v>
+        <v>1475.75</v>
       </c>
       <c r="C13" t="n">
         <v>24</v>
       </c>
       <c r="D13" t="n">
-        <v>1106.05</v>
+        <v>1073.14</v>
       </c>
       <c r="E13" t="n">
-        <v>300.89</v>
+        <v>297.04</v>
       </c>
       <c r="F13" t="n">
-        <v>1490</v>
+        <v>1624</v>
       </c>
       <c r="G13" t="n">
-        <v>381006</v>
+        <v>436946</v>
       </c>
       <c r="H13" t="n">
-        <v>69765</v>
+        <v>67004</v>
       </c>
     </row>
     <row r="14">
@@ -714,25 +714,25 @@
         <v>45698</v>
       </c>
       <c r="B14" t="n">
-        <v>624.1799999999999</v>
+        <v>511.44</v>
       </c>
       <c r="C14" t="n">
-        <v>10.23</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>452.54</v>
+        <v>370.61</v>
       </c>
       <c r="E14" t="n">
-        <v>122.57</v>
+        <v>102.46</v>
       </c>
       <c r="F14" t="n">
-        <v>726</v>
+        <v>519</v>
       </c>
       <c r="G14" t="n">
-        <v>163000</v>
+        <v>153422</v>
       </c>
       <c r="H14" t="n">
-        <v>28728</v>
+        <v>23170</v>
       </c>
     </row>
     <row r="15">
@@ -740,25 +740,25 @@
         <v>45699</v>
       </c>
       <c r="B15" t="n">
-        <v>1425.27</v>
+        <v>1336.36</v>
       </c>
       <c r="C15" t="n">
-        <v>24</v>
+        <v>22.3</v>
       </c>
       <c r="D15" t="n">
-        <v>1034.83</v>
+        <v>965.92</v>
       </c>
       <c r="E15" t="n">
-        <v>277.95</v>
+        <v>260.97</v>
       </c>
       <c r="F15" t="n">
-        <v>1385</v>
+        <v>1375</v>
       </c>
       <c r="G15" t="n">
-        <v>330607</v>
+        <v>343207</v>
       </c>
       <c r="H15" t="n">
-        <v>62698</v>
+        <v>59407</v>
       </c>
     </row>
     <row r="16">
@@ -766,25 +766,25 @@
         <v>45700</v>
       </c>
       <c r="B16" t="n">
-        <v>1437.64</v>
+        <v>1407.02</v>
       </c>
       <c r="C16" t="n">
         <v>24</v>
       </c>
       <c r="D16" t="n">
-        <v>1051.15</v>
+        <v>1020.75</v>
       </c>
       <c r="E16" t="n">
-        <v>293.92</v>
+        <v>284.42</v>
       </c>
       <c r="F16" t="n">
-        <v>1658</v>
+        <v>1555</v>
       </c>
       <c r="G16" t="n">
-        <v>373379</v>
+        <v>369522</v>
       </c>
       <c r="H16" t="n">
-        <v>64689</v>
+        <v>62906</v>
       </c>
     </row>
     <row r="17">
@@ -792,25 +792,25 @@
         <v>45701</v>
       </c>
       <c r="B17" t="n">
-        <v>1397.6</v>
+        <v>1499.3</v>
       </c>
       <c r="C17" t="n">
-        <v>22.01</v>
+        <v>24</v>
       </c>
       <c r="D17" t="n">
-        <v>1016.42</v>
+        <v>1074.16</v>
       </c>
       <c r="E17" t="n">
-        <v>270.02</v>
+        <v>301.36</v>
       </c>
       <c r="F17" t="n">
-        <v>1163</v>
+        <v>1222</v>
       </c>
       <c r="G17" t="n">
-        <v>385725</v>
+        <v>395188</v>
       </c>
       <c r="H17" t="n">
-        <v>66363</v>
+        <v>67287</v>
       </c>
     </row>
     <row r="18">
@@ -818,25 +818,25 @@
         <v>45702</v>
       </c>
       <c r="B18" t="n">
-        <v>1526.88</v>
+        <v>1467.18</v>
       </c>
       <c r="C18" t="n">
-        <v>24</v>
+        <v>23.68</v>
       </c>
       <c r="D18" t="n">
-        <v>1111.87</v>
+        <v>1065.43</v>
       </c>
       <c r="E18" t="n">
-        <v>301.18</v>
+        <v>294.88</v>
       </c>
       <c r="F18" t="n">
-        <v>1291</v>
+        <v>1225</v>
       </c>
       <c r="G18" t="n">
-        <v>377713</v>
+        <v>367976</v>
       </c>
       <c r="H18" t="n">
-        <v>69512</v>
+        <v>65505</v>
       </c>
     </row>
     <row r="19">
@@ -844,25 +844,25 @@
         <v>45703</v>
       </c>
       <c r="B19" t="n">
-        <v>1476.05</v>
+        <v>1463.25</v>
       </c>
       <c r="C19" t="n">
         <v>24</v>
       </c>
       <c r="D19" t="n">
-        <v>1072.39</v>
+        <v>1060.54</v>
       </c>
       <c r="E19" t="n">
-        <v>293.04</v>
+        <v>289.16</v>
       </c>
       <c r="F19" t="n">
-        <v>1460</v>
+        <v>1233</v>
       </c>
       <c r="G19" t="n">
-        <v>381798</v>
+        <v>399814</v>
       </c>
       <c r="H19" t="n">
-        <v>62635</v>
+        <v>63022</v>
       </c>
     </row>
     <row r="20">
@@ -870,25 +870,25 @@
         <v>45704</v>
       </c>
       <c r="B20" t="n">
-        <v>1558.34</v>
+        <v>1377.65</v>
       </c>
       <c r="C20" t="n">
-        <v>24</v>
+        <v>23.15</v>
       </c>
       <c r="D20" t="n">
-        <v>1131.91</v>
+        <v>998.5700000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>312.01</v>
+        <v>272.39</v>
       </c>
       <c r="F20" t="n">
-        <v>1414</v>
+        <v>1261</v>
       </c>
       <c r="G20" t="n">
-        <v>398511</v>
+        <v>396970</v>
       </c>
       <c r="H20" t="n">
-        <v>75464</v>
+        <v>62654</v>
       </c>
     </row>
     <row r="21">
@@ -896,25 +896,25 @@
         <v>45705</v>
       </c>
       <c r="B21" t="n">
-        <v>1480.61</v>
+        <v>1416.06</v>
       </c>
       <c r="C21" t="n">
-        <v>23.14</v>
+        <v>24</v>
       </c>
       <c r="D21" t="n">
-        <v>1064.66</v>
+        <v>1027.48</v>
       </c>
       <c r="E21" t="n">
-        <v>291.83</v>
+        <v>283.12</v>
       </c>
       <c r="F21" t="n">
-        <v>1240</v>
+        <v>1674</v>
       </c>
       <c r="G21" t="n">
-        <v>384387</v>
+        <v>437862</v>
       </c>
       <c r="H21" t="n">
-        <v>68124</v>
+        <v>61594</v>
       </c>
     </row>
     <row r="22">
@@ -922,25 +922,25 @@
         <v>45706</v>
       </c>
       <c r="B22" t="n">
-        <v>1491.77</v>
+        <v>481.61</v>
       </c>
       <c r="C22" t="n">
-        <v>24</v>
+        <v>8.23</v>
       </c>
       <c r="D22" t="n">
-        <v>1090.53</v>
+        <v>352.24</v>
       </c>
       <c r="E22" t="n">
-        <v>299.55</v>
+        <v>97.12</v>
       </c>
       <c r="F22" t="n">
-        <v>1372</v>
+        <v>569</v>
       </c>
       <c r="G22" t="n">
-        <v>385157</v>
+        <v>155035</v>
       </c>
       <c r="H22" t="n">
-        <v>69491</v>
+        <v>23429</v>
       </c>
     </row>
     <row r="23">
@@ -948,25 +948,25 @@
         <v>45707</v>
       </c>
       <c r="B23" t="n">
-        <v>1385.97</v>
+        <v>1486.03</v>
       </c>
       <c r="C23" t="n">
-        <v>22.81</v>
+        <v>24</v>
       </c>
       <c r="D23" t="n">
-        <v>1003.26</v>
+        <v>1062.93</v>
       </c>
       <c r="E23" t="n">
-        <v>279.44</v>
+        <v>301.36</v>
       </c>
       <c r="F23" t="n">
-        <v>1352</v>
+        <v>1557</v>
       </c>
       <c r="G23" t="n">
-        <v>353678</v>
+        <v>362929</v>
       </c>
       <c r="H23" t="n">
-        <v>66130</v>
+        <v>72295</v>
       </c>
     </row>
     <row r="24">
@@ -974,25 +974,25 @@
         <v>45708</v>
       </c>
       <c r="B24" t="n">
-        <v>1444.58</v>
+        <v>1374.5</v>
       </c>
       <c r="C24" t="n">
-        <v>24</v>
+        <v>22.73</v>
       </c>
       <c r="D24" t="n">
-        <v>1042.01</v>
+        <v>993.91</v>
       </c>
       <c r="E24" t="n">
-        <v>287.73</v>
+        <v>279.7</v>
       </c>
       <c r="F24" t="n">
-        <v>1310</v>
+        <v>1100</v>
       </c>
       <c r="G24" t="n">
-        <v>365059</v>
+        <v>374835</v>
       </c>
       <c r="H24" t="n">
-        <v>65656</v>
+        <v>61292</v>
       </c>
     </row>
     <row r="25">
@@ -1000,25 +1000,25 @@
         <v>45709</v>
       </c>
       <c r="B25" t="n">
-        <v>1304.84</v>
+        <v>1426.42</v>
       </c>
       <c r="C25" t="n">
-        <v>20.96</v>
+        <v>23.73</v>
       </c>
       <c r="D25" t="n">
-        <v>955.5599999999999</v>
+        <v>1030</v>
       </c>
       <c r="E25" t="n">
-        <v>267.45</v>
+        <v>284.16</v>
       </c>
       <c r="F25" t="n">
-        <v>1429</v>
+        <v>1279</v>
       </c>
       <c r="G25" t="n">
-        <v>328615</v>
+        <v>414438</v>
       </c>
       <c r="H25" t="n">
-        <v>57148</v>
+        <v>64000</v>
       </c>
     </row>
     <row r="26">
@@ -1026,25 +1026,25 @@
         <v>45710</v>
       </c>
       <c r="B26" t="n">
-        <v>1532.93</v>
+        <v>1463.9</v>
       </c>
       <c r="C26" t="n">
-        <v>24</v>
+        <v>23.31</v>
       </c>
       <c r="D26" t="n">
-        <v>1111.45</v>
+        <v>1063.24</v>
       </c>
       <c r="E26" t="n">
-        <v>305.46</v>
+        <v>286.86</v>
       </c>
       <c r="F26" t="n">
-        <v>1105</v>
+        <v>1251</v>
       </c>
       <c r="G26" t="n">
-        <v>364976</v>
+        <v>422235</v>
       </c>
       <c r="H26" t="n">
-        <v>73309</v>
+        <v>70356</v>
       </c>
     </row>
     <row r="27">
@@ -1052,25 +1052,25 @@
         <v>45711</v>
       </c>
       <c r="B27" t="n">
-        <v>1503.89</v>
+        <v>1518.7</v>
       </c>
       <c r="C27" t="n">
-        <v>23.88</v>
+        <v>23.91</v>
       </c>
       <c r="D27" t="n">
-        <v>1085.25</v>
+        <v>1109.61</v>
       </c>
       <c r="E27" t="n">
-        <v>297.24</v>
+        <v>308.74</v>
       </c>
       <c r="F27" t="n">
-        <v>1377</v>
+        <v>1318</v>
       </c>
       <c r="G27" t="n">
-        <v>397353</v>
+        <v>368086</v>
       </c>
       <c r="H27" t="n">
-        <v>67422</v>
+        <v>62909</v>
       </c>
     </row>
     <row r="28">
@@ -1078,25 +1078,25 @@
         <v>45712</v>
       </c>
       <c r="B28" t="n">
-        <v>1385.89</v>
+        <v>1536.11</v>
       </c>
       <c r="C28" t="n">
-        <v>22.43</v>
+        <v>24</v>
       </c>
       <c r="D28" t="n">
-        <v>1010.34</v>
+        <v>1109.98</v>
       </c>
       <c r="E28" t="n">
-        <v>272.99</v>
+        <v>302.23</v>
       </c>
       <c r="F28" t="n">
-        <v>1283</v>
+        <v>1360</v>
       </c>
       <c r="G28" t="n">
-        <v>372286</v>
+        <v>381106</v>
       </c>
       <c r="H28" t="n">
-        <v>66230</v>
+        <v>70597</v>
       </c>
     </row>
     <row r="29">
@@ -1104,25 +1104,25 @@
         <v>45713</v>
       </c>
       <c r="B29" t="n">
-        <v>1547.09</v>
+        <v>1236.98</v>
       </c>
       <c r="C29" t="n">
-        <v>24</v>
+        <v>20.71</v>
       </c>
       <c r="D29" t="n">
-        <v>1114.13</v>
+        <v>889.26</v>
       </c>
       <c r="E29" t="n">
-        <v>298.72</v>
+        <v>242.58</v>
       </c>
       <c r="F29" t="n">
-        <v>1683</v>
+        <v>1111</v>
       </c>
       <c r="G29" t="n">
-        <v>393803</v>
+        <v>334464</v>
       </c>
       <c r="H29" t="n">
-        <v>67509</v>
+        <v>56651</v>
       </c>
     </row>
     <row r="30">
@@ -1130,25 +1130,25 @@
         <v>45714</v>
       </c>
       <c r="B30" t="n">
-        <v>1388.34</v>
+        <v>1530.19</v>
       </c>
       <c r="C30" t="n">
-        <v>23.12</v>
+        <v>24</v>
       </c>
       <c r="D30" t="n">
-        <v>999.8200000000001</v>
+        <v>1102.79</v>
       </c>
       <c r="E30" t="n">
-        <v>275.53</v>
+        <v>305.04</v>
       </c>
       <c r="F30" t="n">
-        <v>1361</v>
+        <v>1500</v>
       </c>
       <c r="G30" t="n">
-        <v>333373</v>
+        <v>397072</v>
       </c>
       <c r="H30" t="n">
-        <v>61375</v>
+        <v>70569</v>
       </c>
     </row>
     <row r="31">
@@ -1156,25 +1156,25 @@
         <v>45715</v>
       </c>
       <c r="B31" t="n">
-        <v>1410.29</v>
+        <v>1526.09</v>
       </c>
       <c r="C31" t="n">
         <v>24</v>
       </c>
       <c r="D31" t="n">
-        <v>1022.02</v>
+        <v>1114.26</v>
       </c>
       <c r="E31" t="n">
-        <v>277.91</v>
+        <v>305.42</v>
       </c>
       <c r="F31" t="n">
-        <v>1301</v>
+        <v>1069</v>
       </c>
       <c r="G31" t="n">
-        <v>364839</v>
+        <v>424424</v>
       </c>
       <c r="H31" t="n">
-        <v>62313</v>
+        <v>72214</v>
       </c>
     </row>
     <row r="32">
@@ -1182,25 +1182,25 @@
         <v>45716</v>
       </c>
       <c r="B32" t="n">
-        <v>1501.22</v>
+        <v>1527.24</v>
       </c>
       <c r="C32" t="n">
-        <v>23.44</v>
+        <v>24</v>
       </c>
       <c r="D32" t="n">
-        <v>1088.43</v>
+        <v>1114.03</v>
       </c>
       <c r="E32" t="n">
-        <v>296.27</v>
+        <v>313.11</v>
       </c>
       <c r="F32" t="n">
-        <v>1324</v>
+        <v>1391</v>
       </c>
       <c r="G32" t="n">
-        <v>430288</v>
+        <v>431431</v>
       </c>
       <c r="H32" t="n">
-        <v>70682</v>
+        <v>69280</v>
       </c>
     </row>
     <row r="34">
@@ -1210,25 +1210,25 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>40267.85999999999</v>
+        <v>38879.85</v>
       </c>
       <c r="C34" t="n">
-        <v>646.87</v>
+        <v>631.03</v>
       </c>
       <c r="D34" t="n">
-        <v>29206.37</v>
+        <v>28173.89</v>
       </c>
       <c r="E34" t="n">
-        <v>8019.57</v>
+        <v>7742.02</v>
       </c>
       <c r="F34" t="n">
-        <v>37734</v>
+        <v>35807</v>
       </c>
       <c r="G34" t="n">
-        <v>10416699</v>
+        <v>10448067</v>
       </c>
       <c r="H34" t="n">
-        <v>1832391</v>
+        <v>1758332</v>
       </c>
     </row>
   </sheetData>
